--- a/Semiconductor/GSIT.xlsx
+++ b/Semiconductor/GSIT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/Models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E98702-752D-F34A-B11A-6DCC1F8C0DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2132F14A-90D0-7B41-BA9D-3AC35FA42E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23160" yWindow="500" windowWidth="27640" windowHeight="16940" activeTab="1" xr2:uid="{5933BAAC-E1F1-9446-AB0B-858798EE111B}"/>
+    <workbookView xWindow="23160" yWindow="600" windowWidth="27640" windowHeight="16940" xr2:uid="{5933BAAC-E1F1-9446-AB0B-858798EE111B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -60,18 +60,6 @@
     <t>Q324</t>
   </si>
   <si>
-    <t>Q123</t>
-  </si>
-  <si>
-    <t>Q223</t>
-  </si>
-  <si>
-    <t>Q323</t>
-  </si>
-  <si>
-    <t>Q423</t>
-  </si>
-  <si>
     <t>Q124</t>
   </si>
   <si>
@@ -154,6 +142,18 @@
   </si>
   <si>
     <t>$K</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -545,7 +545,7 @@
   <cols>
     <col min="1" max="5" width="10.83203125" style="1"/>
     <col min="6" max="6" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.5" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
@@ -557,29 +557,29 @@
     </row>
     <row r="3" spans="1:8">
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>2.8</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3">
         <v>1995</v>
@@ -588,10 +588,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>25.485510000000001</v>
+        <v>36.186202999999999</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -600,7 +600,7 @@
       </c>
       <c r="G6" s="2">
         <f>+G5*G4</f>
-        <v>71.359427999999994</v>
+        <v>222.18328641999997</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -608,11 +608,11 @@
         <v>3</v>
       </c>
       <c r="G7" s="2">
-        <v>18.356000000000002</v>
+        <v>70.671999999999997</v>
       </c>
       <c r="H7" s="1" t="str">
         <f>+H5</f>
-        <v>Q324</v>
+        <v>Q325</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -624,7 +624,7 @@
       </c>
       <c r="H8" s="1" t="str">
         <f>+H7</f>
-        <v>Q324</v>
+        <v>Q325</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -633,32 +633,36 @@
       </c>
       <c r="G9" s="2">
         <f>+G6-G7+G8</f>
-        <v>53.003427999999992</v>
+        <v>151.51128641999998</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="G11" s="2">
+        <f>+G7/G5</f>
+        <v>1.9530095489709158</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -676,14 +680,14 @@
     <col min="3" max="6" width="5.5" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="13" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16" width="5.5" style="1" customWidth="1"/>
-    <col min="17" max="19" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="38" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="38" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="39" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:38" s="5" customFormat="1">
@@ -714,34 +718,34 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Q3" s="3">
         <v>2022</v>
@@ -833,28 +837,41 @@
     </row>
     <row r="4" spans="1:38">
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="C4" s="6">
+        <v>5587</v>
+      </c>
+      <c r="D4" s="6">
+        <v>5708</v>
+      </c>
+      <c r="E4" s="6">
+        <v>5318</v>
+      </c>
+      <c r="F4" s="6">
+        <v>5152</v>
       </c>
       <c r="G4" s="6">
-        <v>5587</v>
+        <v>4671</v>
       </c>
       <c r="H4" s="6">
-        <v>5708</v>
+        <v>4550</v>
       </c>
       <c r="I4" s="6">
-        <v>5318</v>
-      </c>
-      <c r="J4" s="6">
-        <v>5152</v>
-      </c>
-      <c r="K4" s="6">
-        <v>4671</v>
-      </c>
-      <c r="L4" s="6">
-        <v>4550</v>
-      </c>
-      <c r="M4" s="6">
         <v>5414</v>
+      </c>
+      <c r="J4" s="1">
+        <f>+T4-SUM(G4:I4)</f>
+        <v>5883</v>
+      </c>
+      <c r="K4" s="1">
+        <v>6283</v>
+      </c>
+      <c r="L4" s="1">
+        <v>6444</v>
+      </c>
+      <c r="M4" s="1">
+        <v>6076</v>
       </c>
       <c r="Q4" s="1">
         <v>33384</v>
@@ -864,32 +881,48 @@
       </c>
       <c r="S4" s="1">
         <v>21765</v>
+      </c>
+      <c r="T4" s="1">
+        <v>20518</v>
       </c>
     </row>
     <row r="5" spans="1:38">
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C5" s="1">
+        <v>2518</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2587</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2343</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2494</v>
+      </c>
       <c r="G5" s="1">
-        <v>2518</v>
+        <v>2510</v>
       </c>
       <c r="H5" s="1">
-        <v>2587</v>
+        <v>2793</v>
       </c>
       <c r="I5" s="1">
-        <v>2343</v>
+        <v>2491</v>
       </c>
       <c r="J5" s="1">
-        <v>2494</v>
+        <f t="shared" ref="J5:J13" si="2">+T5-SUM(G5:I5)</f>
+        <v>2584</v>
       </c>
       <c r="K5" s="1">
-        <v>2510</v>
+        <v>2632</v>
       </c>
       <c r="L5" s="1">
-        <v>2793</v>
+        <v>2911</v>
       </c>
       <c r="M5" s="1">
-        <v>2491</v>
+        <v>2876</v>
       </c>
       <c r="Q5" s="1">
         <v>14847</v>
@@ -900,31 +933,47 @@
       <c r="S5" s="1">
         <v>9942</v>
       </c>
+      <c r="T5" s="1">
+        <v>10378</v>
+      </c>
     </row>
     <row r="6" spans="1:38">
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5204</v>
+      </c>
+      <c r="D6" s="1">
+        <v>4691</v>
+      </c>
+      <c r="E6" s="1">
+        <v>6976</v>
+      </c>
+      <c r="F6" s="1">
+        <v>4818</v>
       </c>
       <c r="G6" s="1">
-        <v>5204</v>
+        <v>4214</v>
       </c>
       <c r="H6" s="1">
-        <v>4691</v>
+        <v>4788</v>
       </c>
       <c r="I6" s="1">
-        <v>6976</v>
+        <v>4037</v>
       </c>
       <c r="J6" s="1">
-        <v>4818</v>
+        <f t="shared" si="2"/>
+        <v>2966</v>
       </c>
       <c r="K6" s="1">
-        <v>4214</v>
+        <v>3097</v>
       </c>
       <c r="L6" s="1">
-        <v>4788</v>
+        <v>3768</v>
       </c>
       <c r="M6" s="1">
-        <v>4037</v>
+        <v>7457</v>
       </c>
       <c r="Q6" s="1">
         <v>24672</v>
@@ -935,31 +984,47 @@
       <c r="S6" s="1">
         <v>21689</v>
       </c>
+      <c r="T6" s="1">
+        <v>16005</v>
+      </c>
     </row>
     <row r="7" spans="1:38">
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3004</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2523</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2684</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2354</v>
       </c>
       <c r="G7" s="1">
-        <v>3004</v>
+        <v>2604</v>
       </c>
       <c r="H7" s="1">
-        <v>2523</v>
+        <v>2553</v>
       </c>
       <c r="I7" s="1">
-        <v>2684</v>
+        <v>2997</v>
       </c>
       <c r="J7" s="1">
-        <v>2354</v>
+        <f t="shared" si="2"/>
+        <v>2609</v>
       </c>
       <c r="K7" s="1">
-        <v>2604</v>
+        <v>2730</v>
       </c>
       <c r="L7" s="1">
-        <v>2553</v>
+        <v>2952</v>
       </c>
       <c r="M7" s="1">
-        <v>2997</v>
+        <v>2649</v>
       </c>
       <c r="Q7" s="1">
         <v>10218</v>
@@ -970,38 +1035,57 @@
       <c r="S7" s="1">
         <v>10565</v>
       </c>
+      <c r="T7" s="1">
+        <v>10763</v>
+      </c>
     </row>
     <row r="8" spans="1:38">
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" ref="C8:I8" si="3">+C4-SUM(C5:C7)</f>
+        <v>-5139</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="3"/>
+        <v>-4093</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="3"/>
+        <v>-6685</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="3"/>
+        <v>-4514</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" ref="G8:M8" si="2">+G4-SUM(G5:G7)</f>
-        <v>-5139</v>
+        <f t="shared" si="3"/>
+        <v>-4657</v>
       </c>
       <c r="H8" s="1">
-        <f t="shared" si="2"/>
-        <v>-4093</v>
+        <f t="shared" si="3"/>
+        <v>-5584</v>
       </c>
       <c r="I8" s="1">
-        <f t="shared" si="2"/>
-        <v>-6685</v>
+        <f t="shared" si="3"/>
+        <v>-4111</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" si="2"/>
-        <v>-4514</v>
+        <v>-2276</v>
       </c>
       <c r="K8" s="1">
-        <f t="shared" si="2"/>
-        <v>-4657</v>
+        <f t="shared" ref="K8" si="4">+K4-SUM(K5:K7)</f>
+        <v>-2176</v>
       </c>
       <c r="L8" s="1">
-        <f t="shared" si="2"/>
-        <v>-5584</v>
+        <f t="shared" ref="L8:M8" si="5">+L4-SUM(L5:L7)</f>
+        <v>-3187</v>
       </c>
       <c r="M8" s="1">
-        <f t="shared" si="2"/>
-        <v>-4111</v>
+        <f t="shared" si="5"/>
+        <v>-6906</v>
       </c>
       <c r="Q8" s="1">
         <f>+Q4-SUM(Q5:Q7)</f>
@@ -1015,31 +1099,48 @@
         <f>+S4-SUM(S5:S7)</f>
         <v>-20431</v>
       </c>
+      <c r="T8" s="1">
+        <f>+T4-SUM(T5:T7)</f>
+        <v>-16628</v>
+      </c>
     </row>
     <row r="9" spans="1:38">
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="C9" s="1">
+        <v>143</v>
+      </c>
+      <c r="D9" s="1">
+        <v>131</v>
+      </c>
+      <c r="E9" s="1">
+        <v>155</v>
+      </c>
+      <c r="F9" s="1">
+        <v>108</v>
       </c>
       <c r="G9" s="1">
-        <v>143</v>
+        <v>88</v>
       </c>
       <c r="H9" s="1">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="I9" s="1">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="J9" s="1">
-        <v>108</v>
+        <f t="shared" si="2"/>
+        <v>125</v>
       </c>
       <c r="K9" s="1">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="L9" s="1">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="M9" s="1">
-        <v>70</v>
+        <v>298</v>
       </c>
       <c r="Q9" s="1">
         <v>71</v>
@@ -1050,31 +1151,47 @@
       <c r="S9" s="1">
         <v>541</v>
       </c>
+      <c r="T9" s="1">
+        <v>445</v>
+      </c>
     </row>
     <row r="10" spans="1:38">
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="C10" s="1">
+        <v>-63</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-60</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>-63</v>
+        <v>-33</v>
       </c>
       <c r="H10" s="1">
-        <v>-60</v>
+        <v>-13</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>-73</v>
       </c>
       <c r="K10" s="1">
-        <v>-33</v>
+        <v>-53</v>
       </c>
       <c r="L10" s="1">
-        <v>-13</v>
+        <v>-64</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="Q10" s="1">
         <v>-131</v>
@@ -1085,38 +1202,57 @@
       <c r="S10" s="1">
         <v>-127</v>
       </c>
+      <c r="T10" s="1">
+        <v>-119</v>
+      </c>
     </row>
     <row r="11" spans="1:38">
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" ref="C11:I11" si="6">SUM(C8:C10)</f>
+        <v>-5059</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" si="6"/>
+        <v>-4022</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="6"/>
+        <v>-6530</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" si="6"/>
+        <v>-4406</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" ref="G11:M11" si="3">SUM(G8:G10)</f>
-        <v>-5059</v>
+        <f t="shared" si="6"/>
+        <v>-4602</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="3"/>
-        <v>-4022</v>
+        <f t="shared" si="6"/>
+        <v>-5435</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" si="3"/>
-        <v>-6530</v>
+        <f t="shared" si="6"/>
+        <v>-4041</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="3"/>
-        <v>-4406</v>
+        <f t="shared" si="2"/>
+        <v>-2224</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" si="3"/>
-        <v>-4602</v>
+        <f t="shared" ref="K11" si="7">SUM(K8:K10)</f>
+        <v>-2163</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" si="3"/>
-        <v>-5435</v>
+        <f t="shared" ref="L11:M11" si="8">SUM(L8:L10)</f>
+        <v>-3144</v>
       </c>
       <c r="M11" s="1">
-        <f t="shared" si="3"/>
-        <v>-4041</v>
+        <f t="shared" si="8"/>
+        <v>-6650</v>
       </c>
       <c r="Q11" s="1">
         <f>SUM(Q8:Q10)</f>
@@ -1130,31 +1266,48 @@
         <f>SUM(S8:S10)</f>
         <v>-20017</v>
       </c>
+      <c r="T11" s="1">
+        <f>SUM(T8:T10)</f>
+        <v>-16302</v>
+      </c>
     </row>
     <row r="12" spans="1:38">
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="C12" s="1">
+        <v>51</v>
+      </c>
+      <c r="D12" s="1">
+        <v>33</v>
+      </c>
+      <c r="E12" s="1">
+        <v>71</v>
+      </c>
+      <c r="F12" s="1">
+        <v>-85</v>
       </c>
       <c r="G12" s="1">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H12" s="1">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I12" s="1">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="J12" s="1">
-        <v>-85</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="K12" s="1">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L12" s="1">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="M12" s="1">
-        <v>44</v>
+        <v>-251</v>
       </c>
       <c r="Q12" s="1">
         <v>-45</v>
@@ -1165,38 +1318,57 @@
       <c r="S12" s="1">
         <v>70</v>
       </c>
+      <c r="T12" s="1">
+        <v>130</v>
+      </c>
     </row>
     <row r="13" spans="1:38">
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" ref="C13:I13" si="9">+C11-C12</f>
+        <v>-5110</v>
+      </c>
+      <c r="D13" s="1">
+        <f t="shared" si="9"/>
+        <v>-4055</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="9"/>
+        <v>-6601</v>
+      </c>
+      <c r="F13" s="1">
+        <f t="shared" si="9"/>
+        <v>-4321</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" ref="G13:M13" si="4">+G11-G12</f>
-        <v>-5110</v>
+        <f t="shared" si="9"/>
+        <v>-4659</v>
       </c>
       <c r="H13" s="1">
-        <f t="shared" si="4"/>
-        <v>-4055</v>
+        <f t="shared" si="9"/>
+        <v>-5458</v>
       </c>
       <c r="I13" s="1">
-        <f t="shared" si="4"/>
-        <v>-6601</v>
+        <f t="shared" si="9"/>
+        <v>-4085</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" si="4"/>
-        <v>-4321</v>
+        <f t="shared" si="2"/>
+        <v>-2230</v>
       </c>
       <c r="K13" s="1">
-        <f t="shared" si="4"/>
-        <v>-4659</v>
+        <f t="shared" ref="K13" si="10">+K11-K12</f>
+        <v>-2217</v>
       </c>
       <c r="L13" s="1">
-        <f t="shared" si="4"/>
-        <v>-5458</v>
+        <f t="shared" ref="L13:M13" si="11">+L11-L12</f>
+        <v>-3185</v>
       </c>
       <c r="M13" s="1">
-        <f t="shared" si="4"/>
-        <v>-4085</v>
+        <f t="shared" si="11"/>
+        <v>-6399</v>
       </c>
       <c r="Q13" s="1">
         <f>+Q11-Q12</f>
@@ -1210,22 +1382,26 @@
         <f>+S11-S12</f>
         <v>-20087</v>
       </c>
+      <c r="T13" s="1">
+        <f>+T11-T12</f>
+        <v>-16432</v>
+      </c>
     </row>
     <row r="15" spans="1:38" s="4" customFormat="1">
       <c r="B15" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K15" s="4">
-        <f t="shared" ref="K15:L15" si="5">+K4/G4-1</f>
-        <v>-0.16395203150170035</v>
+        <f>+K4/G4-1</f>
+        <v>0.34510811389424112</v>
       </c>
       <c r="L15" s="4">
-        <f t="shared" si="5"/>
-        <v>-0.20287316047652415</v>
+        <f>+L4/H4-1</f>
+        <v>0.41626373626373625</v>
       </c>
       <c r="M15" s="4">
         <f>+M4/I4-1</f>
-        <v>1.8051899210229427E-2</v>
+        <v>0.12227558182489839</v>
       </c>
       <c r="R15" s="4">
         <f>+R4/Q4-1</f>
@@ -1235,8 +1411,15 @@
         <f>+S4/R4-1</f>
         <v>-0.26694958068101449</v>
       </c>
+      <c r="T15" s="4">
+        <f>+T4/S4-1</f>
+        <v>-5.7293820353779057E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="J4:J14" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>